--- a/data/trans_dic/IP44C$otros_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido algún retraso en otros pagos</t>
+          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,02; 34,8</t>
+          <t>7,63; 37,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 18,11</t>
+          <t>4,37; 19,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,49; 23,95</t>
+          <t>8,04; 23,16</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 32,4</t>
+          <t>4,39; 27,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,77</t>
+          <t>3,29; 6,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 20,34</t>
+          <t>4,51; 16,95</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,64</t>
+          <t>0,26; 3,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,15</t>
+          <t>0,25; 2,25</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 22,83</t>
+          <t>4,49; 23,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,54</t>
+          <t>3,05; 5,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,04</t>
+          <t>4,29; 15,63</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9160</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5803</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14963</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3983; 19442</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2628; 11442</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9033; 26011</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>48313</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24057</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72369</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>19799; 123932</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16591; 34373</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>42998; 161737</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2911</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>388; 5090</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5713</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>809; 7422</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>59082</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31161</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90243</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>29306; 151302</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>22711; 42436</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>59848; 218197</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$otros_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 37,25</t>
+          <t>7,96; 38,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,37; 19,04</t>
+          <t>4,46; 18,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 23,16</t>
+          <t>7,7; 22,4</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 27,49</t>
+          <t>4,61; 30,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,82</t>
+          <t>3,17; 6,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 16,95</t>
+          <t>4,5; 17,55</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,41</t>
+          <t>0,16; 3,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,25</t>
+          <t>0,34; 2,07</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 23,2</t>
+          <t>4,53; 28,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,7</t>
+          <t>3,03; 5,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 15,63</t>
+          <t>4,34; 14,28</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3983; 19442</t>
+          <t>4155; 20077</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2628; 11442</t>
+          <t>2679; 11206</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9033; 26011</t>
+          <t>8647; 25151</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19799; 123932</t>
+          <t>20759; 136957</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16591; 34373</t>
+          <t>15981; 34419</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42998; 161737</t>
+          <t>42994; 167498</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>388; 5090</t>
+          <t>246; 4824</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5713</t>
+          <t>0; 5058</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>809; 7422</t>
+          <t>1134; 6826</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29306; 151302</t>
+          <t>29523; 187081</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22711; 42436</t>
+          <t>22570; 41086</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59848; 218197</t>
+          <t>60653; 199332</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$otros_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 38,46</t>
+          <t>4,97; 20,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 18,65</t>
+          <t>7,49; 26,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,7; 22,4</t>
+          <t>7,61; 20,12</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 30,38</t>
+          <t>3,24; 7,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,83</t>
+          <t>3,98; 8,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 17,55</t>
+          <t>4,04; 6,81</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,23</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,22; 3,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,07</t>
+          <t>0,29; 2,19</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 28,69</t>
+          <t>3,13; 5,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,52</t>
+          <t>3,9; 7,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 14,28</t>
+          <t>3,76; 6,09</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9160</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14963</t>
+          <t>12879</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4155; 20077</t>
+          <t>2727; 11400</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2679; 11206</t>
+          <t>3329; 11804</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8647; 25151</t>
+          <t>7554; 19969</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>48313</t>
+          <t>22583</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24057</t>
+          <t>24645</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72369</t>
+          <t>47228</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20759; 136957</t>
+          <t>15018; 32502</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15981; 34419</t>
+          <t>16839; 35983</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42994; 167498</t>
+          <t>35761; 60319</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>2764</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>246; 4824</t>
+          <t>0; 4885</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5058</t>
+          <t>329; 5410</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1134; 6826</t>
+          <t>909; 6900</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>59082</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>33073</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90243</t>
+          <t>62871</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29523; 187081</t>
+          <t>21413; 39734</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22570; 41086</t>
+          <t>24034; 44862</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60653; 199332</t>
+          <t>48854; 79164</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$otros_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15,59%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12,98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4,97; 20,79</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7,49; 26,57</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7,61; 20,12</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>3,24; 7,02</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3,98; 8,51</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4,04; 6,81</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,95</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,22; 3,62</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,29; 2,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>3,13; 5,82</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3,9; 7,27</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3,76; 6,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.108617113753183</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1558653702528104</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1297644558776571</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5955</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6924</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12879</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.0497319706042746</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.07494490965240787</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.07611113455306154</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2727; 11400</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3329; 11804</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7554; 19969</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.2079315446057476</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.265721774510018</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2012078539653125</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.04879359789838005</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.05828404130977601</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.05332462161823909</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>22583</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>24645</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47228</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.03244877963088921</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.03982316939854333</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.04037682041473844</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>15018; 32502</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>16839; 35983</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>35761; 60319</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.07022512896445494</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.0850971751270963</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.06810553498329451</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.007619292208878799</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.01004852122839109</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.008773007220167146</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2764</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.002197948299209912</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.002886441624619968</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4885</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>329; 5410</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>909; 6900</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.02952613338408727</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.03615408050956802</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.0218994084259649</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.04362333402280392</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.05361046096996077</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.04836267915267855</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>29798</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>33073</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>62871</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.03134814290776823</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.03895843596629513</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.03758021569283367</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>21413; 39734</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>24034; 44862</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>48854; 79164</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.05816785064211902</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.07272110391606745</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.06089613529880177</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>5955</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>6924</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>12879</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2727</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>3329</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>7554</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>11400</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>11804</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>19969</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>22583</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>24645</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>47228</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>15018</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>16839</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>35761</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>32502</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>35983</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>60319</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1260</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1504</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>329</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>4885</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>5410</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>29798</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>33073</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>62871</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>21413</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>24034</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>48854</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>39734</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>44862</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>79164</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>